--- a/data/trans_bre/P16A_n_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A_n_R2-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,0; 18,07</t>
+          <t>10,55; 18,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,69; 17,05</t>
+          <t>9,13; 17,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,09; 22,53</t>
+          <t>12,96; 22,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,5; 22,2</t>
+          <t>11,93; 21,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,98; 57,25</t>
+          <t>29,75; 58,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,64; 37,72</t>
+          <t>17,96; 39,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,27; 57,22</t>
+          <t>28,94; 56,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,98; 46,94</t>
+          <t>22,18; 46,14</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,1; 10,95</t>
+          <t>6,15; 10,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,27; 14,03</t>
+          <t>8,61; 14,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,01; 11,32</t>
+          <t>6,3; 11,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,48; 34,26</t>
+          <t>7,85; 32,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,65; 131,01</t>
+          <t>56,56; 125,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,37; 90,25</t>
+          <t>47,29; 93,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,87; 69,11</t>
+          <t>32,81; 71,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,15; 170,51</t>
+          <t>29,29; 169,09</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,56; 12,1</t>
+          <t>2,15; 12,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 15,46</t>
+          <t>5,24; 15,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 7,14</t>
+          <t>-2,11; 7,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 8,43</t>
+          <t>-1,28; 8,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,03; 119,84</t>
+          <t>13,97; 116,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,63; 145,55</t>
+          <t>33,86; 146,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 48,11</t>
+          <t>-11,57; 56,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 37,43</t>
+          <t>-5,05; 37,36</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,13; 14,29</t>
+          <t>10,28; 14,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,29; 16,85</t>
+          <t>12,49; 16,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,63; 14,3</t>
+          <t>9,71; 14,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,04; 26,91</t>
+          <t>10,11; 27,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,07; 87,17</t>
+          <t>55,17; 85,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,99; 69,81</t>
+          <t>46,99; 70,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,39; 64,9</t>
+          <t>40,39; 64,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,95; 115,43</t>
+          <t>33,94; 116,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A_n_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A_n_R2-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,35</t>
+          <t>19,31</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>40,55%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,55; 18,15</t>
+          <t>10,68; 18,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,13; 17,68</t>
+          <t>9,21; 17,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,96; 22,47</t>
+          <t>12,8; 22,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,93; 21,89</t>
+          <t>14,68; 24,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,75; 58,34</t>
+          <t>29,84; 58,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,96; 39,07</t>
+          <t>18,12; 37,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,94; 56,87</t>
+          <t>28,62; 57,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,18; 46,14</t>
+          <t>29,24; 55,42</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,82</t>
+          <t>7,72</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>29,16%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 10,84</t>
+          <t>6,1; 10,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,61; 14,38</t>
+          <t>8,42; 14,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,3; 11,53</t>
+          <t>6,21; 11,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,85; 32,43</t>
+          <t>5,07; 10,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>56,56; 125,11</t>
+          <t>58,11; 128,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,29; 93,79</t>
+          <t>46,6; 93,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,81; 71,73</t>
+          <t>33,02; 70,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,29; 169,09</t>
+          <t>18,67; 43,06</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,98</t>
+          <t>4,31</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 12,13</t>
+          <t>3,11; 12,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 15,72</t>
+          <t>3,94; 14,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 7,75</t>
+          <t>-2,51; 7,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 8,41</t>
+          <t>0,08; 8,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,97; 116,92</t>
+          <t>21,25; 119,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,86; 146,4</t>
+          <t>23,35; 132,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 56,17</t>
+          <t>-13,57; 52,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 37,36</t>
+          <t>0,28; 39,64</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,55</t>
+          <t>10,8</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,28; 14,27</t>
+          <t>10,24; 14,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,49; 16,99</t>
+          <t>12,15; 16,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,71; 14,09</t>
+          <t>9,72; 14,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,11; 27,82</t>
+          <t>8,67; 12,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,17; 85,78</t>
+          <t>56,14; 86,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,99; 70,02</t>
+          <t>46,46; 70,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,39; 64,33</t>
+          <t>40,37; 64,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,94; 116,13</t>
+          <t>28,04; 44,96</t>
         </is>
       </c>
     </row>
